--- a/templates/DMO_Invoice_Template.xlsx
+++ b/templates/DMO_Invoice_Template.xlsx
@@ -122,7 +122,7 @@
     <t>S/N</t>
   </si>
   <si>
-    <t>Desription</t>
+    <t>Description</t>
   </si>
   <si>
     <t>Unit Price</t>

--- a/templates/DMO_Invoice_Template.xlsx
+++ b/templates/DMO_Invoice_Template.xlsx
@@ -135,7 +135,7 @@
   </si>
   <si>
     <t>1. Claims must be made in respect of shortage or damage within 3 days.
-2. Carriers must also notified in case of damage in transit.
+2. Carriers must also be notified in case of damage in transit.
 3. Interest will be charged on overdue account at 2.5% per month.
 4. Goods sold are not returnable / refundable.
 5. Please notify any discrepancy immediately.
